--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -161,13 +161,22 @@
     <t>狂战士</t>
   </si>
   <si>
-    <t>1</t>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
   </si>
   <si>
     <t>生命越低，伤害越高</t>
   </si>
   <si>
     <t>术士</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>202</t>
   </si>
   <si>
     <t>远程施法，爆发伤害</t>
@@ -1418,7 +1427,9 @@
       <c r="M5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="O5" s="1">
         <v>1</v>
       </c>
@@ -1429,7 +1440,7 @@
         <v>1002</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S5" s="1">
         <v>2101</v>
@@ -1445,7 +1456,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1">
         <v>2001</v>
@@ -1471,8 +1482,12 @@
       <c r="L6" s="3">
         <v>5</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="O6" s="1">
         <v>1</v>
       </c>
@@ -1483,7 +1498,7 @@
         <v>2002</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="S6" s="1">
         <v>2102</v>
@@ -1499,7 +1514,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7" s="1">
         <v>3001</v>
@@ -1537,7 +1552,7 @@
         <v>3002</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="S7" s="1">
         <v>2103</v>
@@ -1553,7 +1568,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E8" s="1">
         <v>4001</v>
@@ -1591,7 +1606,7 @@
         <v>4002</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="S8" s="1">
         <v>2104</v>

--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="58">
   <si>
     <t>#</t>
   </si>
@@ -83,6 +83,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>ShowSkills</t>
+  </si>
+  <si>
     <t>PrefabId</t>
   </si>
   <si>
@@ -152,6 +155,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>创建角色时展示的技能</t>
+  </si>
+  <si>
     <t>预制体资源ID</t>
   </si>
   <si>
@@ -168,6 +174,9 @@
   </si>
   <si>
     <t>生命越低，伤害越高</t>
+  </si>
+  <si>
+    <t>101,102,103,104,105,106,107,108</t>
   </si>
   <si>
     <t>术士</t>
@@ -1162,14 +1171,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="22.1296296296296" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="10" width="10" customWidth="1"/>
@@ -1179,11 +1188,12 @@
     <col min="15" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="34" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="12" customWidth="1"/>
+    <col min="19" max="19" width="35.5555555555556" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1208,8 +1218,9 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1268,137 +1279,146 @@
       <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>20</v>
+      <c r="U3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:20">
+    <row r="4" ht="28.8" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:20">
+    <row r="5" ht="15" customHeight="1" spans="1:21">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1">
         <v>1001</v>
@@ -1425,10 +1445,10 @@
         <v>5</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O5" s="1">
         <v>1</v>
@@ -1440,23 +1460,26 @@
         <v>1002</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" s="1">
+        <v>48</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" s="1">
         <v>2101</v>
       </c>
-      <c r="T5" s="1">
+      <c r="U5" s="1">
         <v>1105</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:20">
+    <row r="6" ht="15" customHeight="1" spans="1:21">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2001</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1">
         <v>2001</v>
@@ -1483,10 +1506,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
@@ -1498,23 +1521,24 @@
         <v>2002</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="S6" s="1">
+        <v>53</v>
+      </c>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1">
         <v>2102</v>
       </c>
-      <c r="T6" s="1">
+      <c r="U6" s="1">
         <v>1106</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:20">
+    <row r="7" ht="15" customHeight="1" spans="1:21">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3001</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1">
         <v>3001</v>
@@ -1552,23 +1576,24 @@
         <v>3002</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S7" s="1">
+        <v>55</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1">
         <v>2103</v>
       </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
         <v>1107</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:20">
+    <row r="8" ht="15" customHeight="1" spans="1:21">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4001</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1">
         <v>4001</v>
@@ -1606,12 +1631,13 @@
         <v>4002</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S8" s="1">
+        <v>57</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1">
         <v>2104</v>
       </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
         <v>1108</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1172,13 +1172,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="22.1296296296296" customWidth="1"/>
+    <col min="5" max="5" width="22.1333333333333" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="10" width="10" customWidth="1"/>
@@ -1188,7 +1188,7 @@
     <col min="15" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="34" customWidth="1"/>
-    <col min="19" max="19" width="35.5555555555556" customWidth="1"/>
+    <col min="19" max="19" width="35.5583333333333" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
   </cols>
@@ -1346,7 +1346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:21">
+    <row r="4" ht="27" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1433,10 +1433,10 @@
         <v>100</v>
       </c>
       <c r="I5" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
         <v>5</v>
@@ -1494,10 +1494,10 @@
         <v>90</v>
       </c>
       <c r="I6" s="1">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J6" s="1">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="K6" s="1">
         <v>5</v>
@@ -1553,10 +1553,10 @@
         <v>100</v>
       </c>
       <c r="I7" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J7" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
@@ -1608,10 +1608,10 @@
         <v>90</v>
       </c>
       <c r="I8" s="1">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J8" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
         <v>5</v>

--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1433,10 +1433,10 @@
         <v>100</v>
       </c>
       <c r="I5" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J5" s="1">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="K5" s="1">
         <v>5</v>

--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -92,6 +92,9 @@
     <t>PortraitId</t>
   </si>
   <si>
+    <t>HeadImgId</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -162,6 +165,9 @@
   </si>
   <si>
     <t>立绘资源ID</t>
+  </si>
+  <si>
+    <t>召唤师头像Id</t>
   </si>
   <si>
     <t>狂战士</t>
@@ -814,12 +820,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1171,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1191,9 +1200,10 @@
     <col min="19" max="19" width="35.5583333333333" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1220,7 +1230,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,143 +1292,152 @@
       <c r="U2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V2" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="U3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="V3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:21">
+    <row r="4" ht="27" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:21">
+    <row r="5" ht="15" customHeight="1" spans="1:22">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1">
         <v>1001</v>
@@ -1441,14 +1460,14 @@
       <c r="K5" s="1">
         <v>5</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="4">
         <v>5</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O5" s="1">
         <v>1</v>
@@ -1460,10 +1479,10 @@
         <v>1002</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T5" s="1">
         <v>2101</v>
@@ -1471,15 +1490,18 @@
       <c r="U5" s="1">
         <v>1105</v>
       </c>
+      <c r="V5">
+        <v>1155</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:21">
+    <row r="6" ht="15" customHeight="1" spans="1:22">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2001</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1">
         <v>2001</v>
@@ -1502,14 +1524,14 @@
       <c r="K6" s="1">
         <v>5</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="4">
         <v>5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
@@ -1521,7 +1543,7 @@
         <v>2002</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1">
@@ -1530,15 +1552,18 @@
       <c r="U6" s="1">
         <v>1106</v>
       </c>
+      <c r="V6">
+        <v>1156</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:21">
+    <row r="7" ht="15" customHeight="1" spans="1:22">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3001</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E7" s="1">
         <v>3001</v>
@@ -1561,7 +1586,7 @@
       <c r="K7" s="1">
         <v>5</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="4">
         <v>5</v>
       </c>
       <c r="M7" s="2"/>
@@ -1576,7 +1601,7 @@
         <v>3002</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="S7" s="1"/>
       <c r="T7" s="1">
@@ -1585,15 +1610,18 @@
       <c r="U7" s="1">
         <v>1107</v>
       </c>
+      <c r="V7">
+        <v>1157</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:21">
+    <row r="8" ht="15" customHeight="1" spans="1:22">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4001</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1">
         <v>4001</v>
@@ -1616,7 +1644,7 @@
       <c r="K8" s="1">
         <v>5</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="4">
         <v>5</v>
       </c>
       <c r="M8" s="2"/>
@@ -1631,7 +1659,7 @@
         <v>4002</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="S8" s="1"/>
       <c r="T8" s="1">
@@ -1639,6 +1667,9 @@
       </c>
       <c r="U8" s="1">
         <v>1108</v>
+      </c>
+      <c r="V8">
+        <v>1158</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -820,15 +820,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1181,13 +1178,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="22.1333333333333" customWidth="1"/>
+    <col min="5" max="5" width="22.1296296296296" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="10" width="10" customWidth="1"/>
@@ -1197,10 +1194,10 @@
     <col min="15" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="34" customWidth="1"/>
-    <col min="19" max="19" width="35.5583333333333" customWidth="1"/>
+    <col min="19" max="19" width="35.5555555555556" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
-    <col min="22" max="22" width="10.375" customWidth="1"/>
+    <col min="22" max="22" width="10.3796296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1362,7 +1359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:22">
+    <row r="4" ht="28.8" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1426,7 +1423,7 @@
       <c r="U4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1460,7 +1457,7 @@
       <c r="K5" s="1">
         <v>5</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>5</v>
       </c>
       <c r="M5" s="2" t="s">
@@ -1524,7 +1521,7 @@
       <c r="K6" s="1">
         <v>5</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>5</v>
       </c>
       <c r="M6" s="2" t="s">
@@ -1586,7 +1583,7 @@
       <c r="K7" s="1">
         <v>5</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="3">
         <v>5</v>
       </c>
       <c r="M7" s="2"/>
@@ -1644,7 +1641,7 @@
       <c r="K8" s="1">
         <v>5</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>5</v>
       </c>
       <c r="M8" s="2"/>

--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1178,13 +1178,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="22.1296296296296" customWidth="1"/>
+    <col min="5" max="5" width="22.1333333333333" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="10" width="10" customWidth="1"/>
@@ -1194,10 +1194,10 @@
     <col min="15" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="34" customWidth="1"/>
-    <col min="19" max="19" width="35.5555555555556" customWidth="1"/>
+    <col min="19" max="19" width="35.5583333333333" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
-    <col min="22" max="22" width="10.3796296296296" customWidth="1"/>
+    <col min="22" max="22" width="10.3833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1359,7 +1359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:22">
+    <row r="4" ht="27" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/SummonerTable.xlsx
+++ b/AAAGameData/DataTables/SummonerTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1449,7 +1449,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J5" s="1">
         <v>40</v>
